--- a/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_frais/trans.alpha.carotene/RANDOMSEARCH_DETAILS_trans.alpha.carotene.xlsx
+++ b/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_frais/trans.alpha.carotene/RANDOMSEARCH_DETAILS_trans.alpha.carotene.xlsx
@@ -413,9 +413,4084 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:H127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Compose</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ID_Pretraitement</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Code_R_Pretraitement</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Meilleurs_Hyperparam_RF</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Rc</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>R2cv</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>RMSEC</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>RMSECV</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('snv',''), list('sder',c(1,3,5))</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0.9723000000000001</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1.424</v>
+      </c>
+      <c r="G2" t="n">
+        <v>93.3627</v>
+      </c>
+      <c r="H2" t="n">
+        <v>229.4133</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0.9839</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1.4597</v>
+      </c>
+      <c r="G3" t="n">
+        <v>85.8604</v>
+      </c>
+      <c r="H3" t="n">
+        <v>238.8598</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1))</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9772999999999999</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.5416</v>
+      </c>
+      <c r="G4" t="n">
+        <v>92.4495</v>
+      </c>
+      <c r="H4" t="n">
+        <v>259.2781</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>list('adj',''),list('red',c(950,700,1)),list('snv','')</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0.7649</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2.0661</v>
+      </c>
+      <c r="G5" t="n">
+        <v>252.8296</v>
+      </c>
+      <c r="H5" t="n">
+        <v>363.7639</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>list('adj',''),list('red',c(950,750,1)),list('snv','')</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>0.7641</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2.063</v>
+      </c>
+      <c r="G6" t="n">
+        <v>252.422</v>
+      </c>
+      <c r="H6" t="n">
+        <v>363.238</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1000,1)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>0.9097</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.5661</v>
+      </c>
+      <c r="G7" t="n">
+        <v>156.6865</v>
+      </c>
+      <c r="H7" t="n">
+        <v>265.0811</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>0.9223</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.4722</v>
+      </c>
+      <c r="G8" t="n">
+        <v>141.1424</v>
+      </c>
+      <c r="H8" t="n">
+        <v>242.0917</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>8</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1200,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0.9756</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.4439</v>
+      </c>
+      <c r="G9" t="n">
+        <v>92.2286</v>
+      </c>
+      <c r="H9" t="n">
+        <v>234.7231</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>9</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 2, 9))</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>0.917</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.5031</v>
+      </c>
+      <c r="G10" t="n">
+        <v>146.6993</v>
+      </c>
+      <c r="H10" t="n">
+        <v>249.8867</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>10</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 2, 15))</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>0.9135</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.5126</v>
+      </c>
+      <c r="G11" t="n">
+        <v>149.1506</v>
+      </c>
+      <c r="H11" t="n">
+        <v>252.2352</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>11</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 2, 21))</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>0.9127</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.5119</v>
+      </c>
+      <c r="G12" t="n">
+        <v>149.7073</v>
+      </c>
+      <c r="H12" t="n">
+        <v>252.0566</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>12</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 2, 31))</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>0.9126</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.5164</v>
+      </c>
+      <c r="G13" t="n">
+        <v>149.7724</v>
+      </c>
+      <c r="H13" t="n">
+        <v>253.1749</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>13</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>0.9137</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.5072</v>
+      </c>
+      <c r="G14" t="n">
+        <v>148.7983</v>
+      </c>
+      <c r="H14" t="n">
+        <v>250.9189</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>14</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>0.9133</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.5054</v>
+      </c>
+      <c r="G15" t="n">
+        <v>148.9218</v>
+      </c>
+      <c r="H15" t="n">
+        <v>250.4531</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>15</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 3, 25))</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>0.9103</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.5155</v>
+      </c>
+      <c r="G16" t="n">
+        <v>151.0303</v>
+      </c>
+      <c r="H16" t="n">
+        <v>252.9523</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>16</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 3, 31))</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>0.9107</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.5178</v>
+      </c>
+      <c r="G17" t="n">
+        <v>150.8909</v>
+      </c>
+      <c r="H17" t="n">
+        <v>253.5076</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>17</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 5))</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>0.9813</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.4402</v>
+      </c>
+      <c r="G18" t="n">
+        <v>81.17189999999999</v>
+      </c>
+      <c r="H18" t="n">
+        <v>233.7493</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>18</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 9))</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>0.9684</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.4273</v>
+      </c>
+      <c r="G19" t="n">
+        <v>96.0209</v>
+      </c>
+      <c r="H19" t="n">
+        <v>230.3034</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>19</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 11))</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>0.9739</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.4162</v>
+      </c>
+      <c r="G20" t="n">
+        <v>91.98269999999999</v>
+      </c>
+      <c r="H20" t="n">
+        <v>227.2931</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>20</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 15))</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>0.9762999999999999</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.3556</v>
+      </c>
+      <c r="G21" t="n">
+        <v>86.7055</v>
+      </c>
+      <c r="H21" t="n">
+        <v>210.0918</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>21</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 21))</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>0.9814000000000001</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1.282</v>
+      </c>
+      <c r="G22" t="n">
+        <v>76.39700000000001</v>
+      </c>
+      <c r="H22" t="n">
+        <v>187.1045</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>22</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 25))</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>0.9855</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.2989</v>
+      </c>
+      <c r="G23" t="n">
+        <v>67.52809999999999</v>
+      </c>
+      <c r="H23" t="n">
+        <v>192.6161</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>23</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 31))</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9788</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.3145</v>
+      </c>
+      <c r="G24" t="n">
+        <v>79.3497</v>
+      </c>
+      <c r="H24" t="n">
+        <v>197.5888</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>24</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 2, 35))</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>0.974</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.3615</v>
+      </c>
+      <c r="G25" t="n">
+        <v>85.99809999999999</v>
+      </c>
+      <c r="H25" t="n">
+        <v>211.818</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>25</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 5))</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>0.971</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.4295</v>
+      </c>
+      <c r="G26" t="n">
+        <v>94.483</v>
+      </c>
+      <c r="H26" t="n">
+        <v>230.8981</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>26</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 9))</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>0.9798</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.4437</v>
+      </c>
+      <c r="G27" t="n">
+        <v>83.46599999999999</v>
+      </c>
+      <c r="H27" t="n">
+        <v>234.6887</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>27</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 11))</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>0.9734</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.4344</v>
+      </c>
+      <c r="G28" t="n">
+        <v>90.9182</v>
+      </c>
+      <c r="H28" t="n">
+        <v>232.1916</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>28</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>0.9738</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.4451</v>
+      </c>
+      <c r="G29" t="n">
+        <v>91.7435</v>
+      </c>
+      <c r="H29" t="n">
+        <v>235.0398</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>29</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>0.9754</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.4072</v>
+      </c>
+      <c r="G30" t="n">
+        <v>88.8998</v>
+      </c>
+      <c r="H30" t="n">
+        <v>224.804</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>30</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 25))</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>0.9772</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1.3694</v>
+      </c>
+      <c r="G31" t="n">
+        <v>86.0838</v>
+      </c>
+      <c r="H31" t="n">
+        <v>214.1133</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>31</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 31))</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>0.9774</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1.3439</v>
+      </c>
+      <c r="G32" t="n">
+        <v>84.58069999999999</v>
+      </c>
+      <c r="H32" t="n">
+        <v>206.6036</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>32</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1, 3, 35))</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>0.9778</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1.3457</v>
+      </c>
+      <c r="G33" t="n">
+        <v>84.0839</v>
+      </c>
+      <c r="H33" t="n">
+        <v>207.1352</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>33</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 2, 9))</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>0.9739</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1.516</v>
+      </c>
+      <c r="G34" t="n">
+        <v>98.425</v>
+      </c>
+      <c r="H34" t="n">
+        <v>253.0774</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>34</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 2, 11))</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>0.9727</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1.4987</v>
+      </c>
+      <c r="G35" t="n">
+        <v>103.4145</v>
+      </c>
+      <c r="H35" t="n">
+        <v>248.7952</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>35</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 2, 15))</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>0.977</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1.4535</v>
+      </c>
+      <c r="G36" t="n">
+        <v>91.57810000000001</v>
+      </c>
+      <c r="H36" t="n">
+        <v>237.2451</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>36</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 2, 21))</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>0.9742</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1.4271</v>
+      </c>
+      <c r="G37" t="n">
+        <v>94.56</v>
+      </c>
+      <c r="H37" t="n">
+        <v>230.2553</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>37</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 2, 25))</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>0.982</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1.4214</v>
+      </c>
+      <c r="G38" t="n">
+        <v>80.5214</v>
+      </c>
+      <c r="H38" t="n">
+        <v>228.6918</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>38</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 2, 31))</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>0.9749</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1.4162</v>
+      </c>
+      <c r="G39" t="n">
+        <v>90.28270000000001</v>
+      </c>
+      <c r="H39" t="n">
+        <v>227.2819</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>39</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 2, 35))</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>0.9818</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1.4221</v>
+      </c>
+      <c r="G40" t="n">
+        <v>77.70950000000001</v>
+      </c>
+      <c r="H40" t="n">
+        <v>228.8873</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>40</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 3, 9))</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>0.9834000000000001</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1.5183</v>
+      </c>
+      <c r="G41" t="n">
+        <v>88.16759999999999</v>
+      </c>
+      <c r="H41" t="n">
+        <v>253.6345</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>41</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 3, 11))</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>0.974</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1.4967</v>
+      </c>
+      <c r="G42" t="n">
+        <v>97.77070000000001</v>
+      </c>
+      <c r="H42" t="n">
+        <v>248.3072</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>42</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>0.977</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1.4538</v>
+      </c>
+      <c r="G43" t="n">
+        <v>91.7924</v>
+      </c>
+      <c r="H43" t="n">
+        <v>237.341</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>43</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>0.9743000000000001</v>
+      </c>
+      <c r="F44" t="n">
+        <v>1.423</v>
+      </c>
+      <c r="G44" t="n">
+        <v>93.946</v>
+      </c>
+      <c r="H44" t="n">
+        <v>229.1359</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>44</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 3, 25))</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>0.9819</v>
+      </c>
+      <c r="F45" t="n">
+        <v>1.4187</v>
+      </c>
+      <c r="G45" t="n">
+        <v>80.681</v>
+      </c>
+      <c r="H45" t="n">
+        <v>227.9688</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>45</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 3, 31))</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>0.9736</v>
+      </c>
+      <c r="F46" t="n">
+        <v>1.4275</v>
+      </c>
+      <c r="G46" t="n">
+        <v>92.1026</v>
+      </c>
+      <c r="H46" t="n">
+        <v>230.3525</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>46</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2, 3, 35))</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>0.9826</v>
+      </c>
+      <c r="F47" t="n">
+        <v>1.435</v>
+      </c>
+      <c r="G47" t="n">
+        <v>76.8366</v>
+      </c>
+      <c r="H47" t="n">
+        <v>232.3625</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>47</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1400,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>0.9752</v>
+      </c>
+      <c r="F48" t="n">
+        <v>1.4727</v>
+      </c>
+      <c r="G48" t="n">
+        <v>94.1597</v>
+      </c>
+      <c r="H48" t="n">
+        <v>242.2113</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>48</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>list('adj',''),list('red',c(40,1300,1)),list('snv',''),list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>0.9761</v>
+      </c>
+      <c r="F49" t="n">
+        <v>1.4473</v>
+      </c>
+      <c r="G49" t="n">
+        <v>92.15089999999999</v>
+      </c>
+      <c r="H49" t="n">
+        <v>235.635</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>49</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(800,750,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>0.9119</v>
+      </c>
+      <c r="F50" t="n">
+        <v>1.9523</v>
+      </c>
+      <c r="G50" t="n">
+        <v>209.3237</v>
+      </c>
+      <c r="H50" t="n">
+        <v>343.8104</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>50</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(800,1100,1)), list('snv',''), list('sder',c(1,3,11))</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>0.877</v>
+      </c>
+      <c r="F51" t="n">
+        <v>1.9372</v>
+      </c>
+      <c r="G51" t="n">
+        <v>214.556</v>
+      </c>
+      <c r="H51" t="n">
+        <v>341.0743</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>51</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(800,1100,1)), list('snv',''), list('sder',c(1,3,15))</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>0.8506</v>
+      </c>
+      <c r="F52" t="n">
+        <v>1.9508</v>
+      </c>
+      <c r="G52" t="n">
+        <v>233.4296</v>
+      </c>
+      <c r="H52" t="n">
+        <v>343.5357</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>52</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(800,1100,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>0.9021</v>
+      </c>
+      <c r="F53" t="n">
+        <v>1.9178</v>
+      </c>
+      <c r="G53" t="n">
+        <v>213.8773</v>
+      </c>
+      <c r="H53" t="n">
+        <v>337.5124</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>53</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(800,1100,1)), list('snv',''), list('sder',c(2,3,21))</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>0.9097</v>
+      </c>
+      <c r="F54" t="n">
+        <v>1.924</v>
+      </c>
+      <c r="G54" t="n">
+        <v>202.1652</v>
+      </c>
+      <c r="H54" t="n">
+        <v>338.6537</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>54</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>list('adj',''),list('red',c(950,20,1)),list('snv',''),list('sder',c(1,3,15))</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>0.9082</v>
+      </c>
+      <c r="F55" t="n">
+        <v>1.9726</v>
+      </c>
+      <c r="G55" t="n">
+        <v>207.6191</v>
+      </c>
+      <c r="H55" t="n">
+        <v>347.4456</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>55</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>list('adj',''),list('red',c(950,20,1)),list('snv',''),list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>0.9326</v>
+      </c>
+      <c r="F56" t="n">
+        <v>1.9764</v>
+      </c>
+      <c r="G56" t="n">
+        <v>211.907</v>
+      </c>
+      <c r="H56" t="n">
+        <v>348.1214</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>56</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,650,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>0.8956</v>
+      </c>
+      <c r="F57" t="n">
+        <v>1.9988</v>
+      </c>
+      <c r="G57" t="n">
+        <v>226.0602</v>
+      </c>
+      <c r="H57" t="n">
+        <v>352.0956</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>57</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0,3,15))</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>0.7635</v>
+      </c>
+      <c r="F58" t="n">
+        <v>2.0608</v>
+      </c>
+      <c r="G58" t="n">
+        <v>252.5761</v>
+      </c>
+      <c r="H58" t="n">
+        <v>362.8539</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>58</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0,3,21))</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>0.7641</v>
+      </c>
+      <c r="F59" t="n">
+        <v>2.0563</v>
+      </c>
+      <c r="G59" t="n">
+        <v>252.5934</v>
+      </c>
+      <c r="H59" t="n">
+        <v>362.0933</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>59</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0,3,25))</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>0.7627</v>
+      </c>
+      <c r="F60" t="n">
+        <v>2.0567</v>
+      </c>
+      <c r="G60" t="n">
+        <v>252.9306</v>
+      </c>
+      <c r="H60" t="n">
+        <v>362.1641</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>60</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0,3,31))</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>0.7634</v>
+      </c>
+      <c r="F61" t="n">
+        <v>2.059</v>
+      </c>
+      <c r="G61" t="n">
+        <v>252.8199</v>
+      </c>
+      <c r="H61" t="n">
+        <v>362.5456</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>61</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(1,3,11))</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>0.8351</v>
+      </c>
+      <c r="F62" t="n">
+        <v>2.0334</v>
+      </c>
+      <c r="G62" t="n">
+        <v>236.5533</v>
+      </c>
+      <c r="H62" t="n">
+        <v>358.1365</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>62</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(1,3,15))</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>0.8286</v>
+      </c>
+      <c r="F63" t="n">
+        <v>2.0251</v>
+      </c>
+      <c r="G63" t="n">
+        <v>237.5554</v>
+      </c>
+      <c r="H63" t="n">
+        <v>356.6978</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>63</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(1,3,21))</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>0.8222</v>
+      </c>
+      <c r="F64" t="n">
+        <v>2.0324</v>
+      </c>
+      <c r="G64" t="n">
+        <v>236.9788</v>
+      </c>
+      <c r="H64" t="n">
+        <v>357.9793</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>64</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(1,3,31))</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>0.8118</v>
+      </c>
+      <c r="F65" t="n">
+        <v>2.0308</v>
+      </c>
+      <c r="G65" t="n">
+        <v>238.2407</v>
+      </c>
+      <c r="H65" t="n">
+        <v>357.6918</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>65</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>0.8927</v>
+      </c>
+      <c r="F66" t="n">
+        <v>2.0028</v>
+      </c>
+      <c r="G66" t="n">
+        <v>226.1244</v>
+      </c>
+      <c r="H66" t="n">
+        <v>352.7958</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>66</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1000,700,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>0.9082</v>
+      </c>
+      <c r="F67" t="n">
+        <v>1.9844</v>
+      </c>
+      <c r="G67" t="n">
+        <v>214.4214</v>
+      </c>
+      <c r="H67" t="n">
+        <v>349.5519</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>67</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1000,750,1)), list('snv',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>0.9102</v>
+      </c>
+      <c r="F68" t="n">
+        <v>1.993</v>
+      </c>
+      <c r="G68" t="n">
+        <v>213.4904</v>
+      </c>
+      <c r="H68" t="n">
+        <v>351.0813</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>72</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,2,11)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>0.9792</v>
+      </c>
+      <c r="F69" t="n">
+        <v>1.3479</v>
+      </c>
+      <c r="G69" t="n">
+        <v>82.7591</v>
+      </c>
+      <c r="H69" t="n">
+        <v>207.8076</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>73</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,2,15)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>0.9831</v>
+      </c>
+      <c r="F70" t="n">
+        <v>1.324</v>
+      </c>
+      <c r="G70" t="n">
+        <v>72.82729999999999</v>
+      </c>
+      <c r="H70" t="n">
+        <v>200.5311</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>74</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,3,15)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>0.975</v>
+      </c>
+      <c r="F71" t="n">
+        <v>1.3908</v>
+      </c>
+      <c r="G71" t="n">
+        <v>90.1444</v>
+      </c>
+      <c r="H71" t="n">
+        <v>220.241</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>75</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,3,21)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>0.9827</v>
+      </c>
+      <c r="F72" t="n">
+        <v>1.3634</v>
+      </c>
+      <c r="G72" t="n">
+        <v>76.25700000000001</v>
+      </c>
+      <c r="H72" t="n">
+        <v>212.3687</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>76</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(2,3,15)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>0.982</v>
+      </c>
+      <c r="F73" t="n">
+        <v>1.4836</v>
+      </c>
+      <c r="G73" t="n">
+        <v>84.96420000000001</v>
+      </c>
+      <c r="H73" t="n">
+        <v>245.0072</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>77</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(2,3,21)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>0.9721</v>
+      </c>
+      <c r="F74" t="n">
+        <v>1.4357</v>
+      </c>
+      <c r="G74" t="n">
+        <v>97.7123</v>
+      </c>
+      <c r="H74" t="n">
+        <v>232.551</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>78</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2')</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>0.9201</v>
+      </c>
+      <c r="F75" t="n">
+        <v>1.5616</v>
+      </c>
+      <c r="G75" t="n">
+        <v>147.7631</v>
+      </c>
+      <c r="H75" t="n">
+        <v>264.0132</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>79</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','3')</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>0.9201</v>
+      </c>
+      <c r="F76" t="n">
+        <v>1.5616</v>
+      </c>
+      <c r="G76" t="n">
+        <v>147.7631</v>
+      </c>
+      <c r="H76" t="n">
+        <v>264.0132</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>80</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2')</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>0.8270999999999999</v>
+      </c>
+      <c r="F77" t="n">
+        <v>2.0458</v>
+      </c>
+      <c r="G77" t="n">
+        <v>228.0066</v>
+      </c>
+      <c r="H77" t="n">
+        <v>360.2827</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>81</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(0, 2, 21))</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>0.8275</v>
+      </c>
+      <c r="F78" t="n">
+        <v>2.0549</v>
+      </c>
+      <c r="G78" t="n">
+        <v>228.6252</v>
+      </c>
+      <c r="H78" t="n">
+        <v>361.8529</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>82</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(0, 2, 25))</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>0.8275</v>
+      </c>
+      <c r="F79" t="n">
+        <v>2.0552</v>
+      </c>
+      <c r="G79" t="n">
+        <v>229.0747</v>
+      </c>
+      <c r="H79" t="n">
+        <v>361.9083</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>83</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(0, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>0.8267</v>
+      </c>
+      <c r="F80" t="n">
+        <v>2.0541</v>
+      </c>
+      <c r="G80" t="n">
+        <v>228.8719</v>
+      </c>
+      <c r="H80" t="n">
+        <v>361.7198</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>84</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 9))</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>0.893</v>
+      </c>
+      <c r="F81" t="n">
+        <v>1.9743</v>
+      </c>
+      <c r="G81" t="n">
+        <v>209.4573</v>
+      </c>
+      <c r="H81" t="n">
+        <v>347.7539</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>85</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>0.8601</v>
+      </c>
+      <c r="F82" t="n">
+        <v>1.987</v>
+      </c>
+      <c r="G82" t="n">
+        <v>231.9082</v>
+      </c>
+      <c r="H82" t="n">
+        <v>350.0103</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>86</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(0, 2, 21))</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>0.9212</v>
+      </c>
+      <c r="F83" t="n">
+        <v>1.5497</v>
+      </c>
+      <c r="G83" t="n">
+        <v>147.386</v>
+      </c>
+      <c r="H83" t="n">
+        <v>261.2025</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>87</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(0, 2, 25))</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>0.9208</v>
+      </c>
+      <c r="F84" t="n">
+        <v>1.5495</v>
+      </c>
+      <c r="G84" t="n">
+        <v>147.7006</v>
+      </c>
+      <c r="H84" t="n">
+        <v>261.1516</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>88</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(0, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>0.9204</v>
+      </c>
+      <c r="F85" t="n">
+        <v>1.5498</v>
+      </c>
+      <c r="G85" t="n">
+        <v>147.9593</v>
+      </c>
+      <c r="H85" t="n">
+        <v>261.2354</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>89</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 9))</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>0.9742</v>
+      </c>
+      <c r="F86" t="n">
+        <v>1.4171</v>
+      </c>
+      <c r="G86" t="n">
+        <v>89.32259999999999</v>
+      </c>
+      <c r="H86" t="n">
+        <v>227.5229</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>90</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 11))</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>0.9722</v>
+      </c>
+      <c r="F87" t="n">
+        <v>1.4303</v>
+      </c>
+      <c r="G87" t="n">
+        <v>93.01439999999999</v>
+      </c>
+      <c r="H87" t="n">
+        <v>231.0967</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>91</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>0.9824000000000001</v>
+      </c>
+      <c r="F88" t="n">
+        <v>1.4432</v>
+      </c>
+      <c r="G88" t="n">
+        <v>77.60899999999999</v>
+      </c>
+      <c r="H88" t="n">
+        <v>234.5314</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>92</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>0.9811</v>
+      </c>
+      <c r="F89" t="n">
+        <v>1.4196</v>
+      </c>
+      <c r="G89" t="n">
+        <v>78.48180000000001</v>
+      </c>
+      <c r="H89" t="n">
+        <v>228.209</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>93</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(2, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>0.9769</v>
+      </c>
+      <c r="F90" t="n">
+        <v>1.454</v>
+      </c>
+      <c r="G90" t="n">
+        <v>91.81699999999999</v>
+      </c>
+      <c r="H90" t="n">
+        <v>237.3748</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>94</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(2, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>0.9743000000000001</v>
+      </c>
+      <c r="F91" t="n">
+        <v>1.423</v>
+      </c>
+      <c r="G91" t="n">
+        <v>93.96639999999999</v>
+      </c>
+      <c r="H91" t="n">
+        <v>229.132</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>95</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','3'), list('sder',c(1, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>0.9824000000000001</v>
+      </c>
+      <c r="F92" t="n">
+        <v>1.4432</v>
+      </c>
+      <c r="G92" t="n">
+        <v>77.60899999999999</v>
+      </c>
+      <c r="H92" t="n">
+        <v>234.5314</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>96</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','3'), list('sder',c(2, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>0.9743000000000001</v>
+      </c>
+      <c r="F93" t="n">
+        <v>1.423</v>
+      </c>
+      <c r="G93" t="n">
+        <v>93.96639999999999</v>
+      </c>
+      <c r="H93" t="n">
+        <v>229.132</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>97</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc','')</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>0.9772999999999999</v>
+      </c>
+      <c r="F94" t="n">
+        <v>1.5416</v>
+      </c>
+      <c r="G94" t="n">
+        <v>92.4495</v>
+      </c>
+      <c r="H94" t="n">
+        <v>259.2781</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>98</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('msc','')</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>0.728</v>
+      </c>
+      <c r="F95" t="n">
+        <v>2.0595</v>
+      </c>
+      <c r="G95" t="n">
+        <v>264.4096</v>
+      </c>
+      <c r="H95" t="n">
+        <v>362.632</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>99</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(0, 2, 15))</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>0.9781</v>
+      </c>
+      <c r="F96" t="n">
+        <v>1.5418</v>
+      </c>
+      <c r="G96" t="n">
+        <v>92.9954</v>
+      </c>
+      <c r="H96" t="n">
+        <v>259.3289</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>100</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(0, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>0.9786</v>
+      </c>
+      <c r="F97" t="n">
+        <v>1.5395</v>
+      </c>
+      <c r="G97" t="n">
+        <v>92.209</v>
+      </c>
+      <c r="H97" t="n">
+        <v>258.7726</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>101</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 5))</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>0.9802999999999999</v>
+      </c>
+      <c r="F98" t="n">
+        <v>1.4445</v>
+      </c>
+      <c r="G98" t="n">
+        <v>82.7825</v>
+      </c>
+      <c r="H98" t="n">
+        <v>234.8903</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>102</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 11))</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>0.9811</v>
+      </c>
+      <c r="F99" t="n">
+        <v>1.3776</v>
+      </c>
+      <c r="G99" t="n">
+        <v>78.70869999999999</v>
+      </c>
+      <c r="H99" t="n">
+        <v>216.4851</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>103</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 15))</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>0.9747</v>
+      </c>
+      <c r="F100" t="n">
+        <v>1.3651</v>
+      </c>
+      <c r="G100" t="n">
+        <v>88.2054</v>
+      </c>
+      <c r="H100" t="n">
+        <v>212.8775</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>104</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 21))</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>0.9761</v>
+      </c>
+      <c r="F101" t="n">
+        <v>1.3372</v>
+      </c>
+      <c r="G101" t="n">
+        <v>84.2809</v>
+      </c>
+      <c r="H101" t="n">
+        <v>204.5685</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>105</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 31))</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>0.9736</v>
+      </c>
+      <c r="F102" t="n">
+        <v>1.3863</v>
+      </c>
+      <c r="G102" t="n">
+        <v>89.9252</v>
+      </c>
+      <c r="H102" t="n">
+        <v>218.9845</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>106</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 5))</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>0.9731</v>
+      </c>
+      <c r="F103" t="n">
+        <v>1.4741</v>
+      </c>
+      <c r="G103" t="n">
+        <v>97.0878</v>
+      </c>
+      <c r="H103" t="n">
+        <v>242.5779</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>107</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 11))</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>0.9814000000000001</v>
+      </c>
+      <c r="F104" t="n">
+        <v>1.4518</v>
+      </c>
+      <c r="G104" t="n">
+        <v>82.9134</v>
+      </c>
+      <c r="H104" t="n">
+        <v>236.8091</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>108</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>0.9826</v>
+      </c>
+      <c r="F105" t="n">
+        <v>1.4345</v>
+      </c>
+      <c r="G105" t="n">
+        <v>79.16240000000001</v>
+      </c>
+      <c r="H105" t="n">
+        <v>232.2231</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>109</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>0.973</v>
+      </c>
+      <c r="F106" t="n">
+        <v>1.3845</v>
+      </c>
+      <c r="G106" t="n">
+        <v>91.8643</v>
+      </c>
+      <c r="H106" t="n">
+        <v>218.4622</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>110</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 31))</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>0.9755</v>
+      </c>
+      <c r="F107" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="G107" t="n">
+        <v>86.95910000000001</v>
+      </c>
+      <c r="H107" t="n">
+        <v>211.3758</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>111</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 2, 11))</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>0.9708</v>
+      </c>
+      <c r="F108" t="n">
+        <v>1.5284</v>
+      </c>
+      <c r="G108" t="n">
+        <v>102.1559</v>
+      </c>
+      <c r="H108" t="n">
+        <v>256.0956</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>112</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 2, 15))</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>0.9812</v>
+      </c>
+      <c r="F109" t="n">
+        <v>1.4462</v>
+      </c>
+      <c r="G109" t="n">
+        <v>82.7079</v>
+      </c>
+      <c r="H109" t="n">
+        <v>235.3326</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>113</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 2, 21))</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>0.9823</v>
+      </c>
+      <c r="F110" t="n">
+        <v>1.4294</v>
+      </c>
+      <c r="G110" t="n">
+        <v>80.7128</v>
+      </c>
+      <c r="H110" t="n">
+        <v>230.8533</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>114</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 2, 31))</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>0.9805</v>
+      </c>
+      <c r="F111" t="n">
+        <v>1.3956</v>
+      </c>
+      <c r="G111" t="n">
+        <v>79.976</v>
+      </c>
+      <c r="H111" t="n">
+        <v>221.5791</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>115</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 3, 11))</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>0.9712</v>
+      </c>
+      <c r="F112" t="n">
+        <v>1.527</v>
+      </c>
+      <c r="G112" t="n">
+        <v>101.7312</v>
+      </c>
+      <c r="H112" t="n">
+        <v>255.757</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>116</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 3, 15))</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>0.9814000000000001</v>
+      </c>
+      <c r="F113" t="n">
+        <v>1.4475</v>
+      </c>
+      <c r="G113" t="n">
+        <v>81.52970000000001</v>
+      </c>
+      <c r="H113" t="n">
+        <v>235.6789</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>117</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 3, 21))</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>0.9818</v>
+      </c>
+      <c r="F114" t="n">
+        <v>1.4215</v>
+      </c>
+      <c r="G114" t="n">
+        <v>81.01479999999999</v>
+      </c>
+      <c r="H114" t="n">
+        <v>228.723</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>118</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 3, 31))</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>0.9715</v>
+      </c>
+      <c r="F115" t="n">
+        <v>1.3973</v>
+      </c>
+      <c r="G115" t="n">
+        <v>94.6212</v>
+      </c>
+      <c r="H115" t="n">
+        <v>222.0556</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>119</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('msc',''), list('sder',c(1,3,15))</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>0.9532</v>
+      </c>
+      <c r="F116" t="n">
+        <v>2.0058</v>
+      </c>
+      <c r="G116" t="n">
+        <v>157.8821</v>
+      </c>
+      <c r="H116" t="n">
+        <v>353.3325</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>120</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(950,750,1)), list('msc',''), list('sder',c(1,3,21))</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>0.854</v>
+      </c>
+      <c r="F117" t="n">
+        <v>2.0085</v>
+      </c>
+      <c r="G117" t="n">
+        <v>228.8811</v>
+      </c>
+      <c r="H117" t="n">
+        <v>353.8</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>121</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,3,15)), list('msc','')</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>0.9826</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.4345</v>
+      </c>
+      <c r="G118" t="n">
+        <v>79.16240000000001</v>
+      </c>
+      <c r="H118" t="n">
+        <v>232.2231</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>122</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(2,3,15)), list('msc','')</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>0.9814000000000001</v>
+      </c>
+      <c r="F119" t="n">
+        <v>1.4475</v>
+      </c>
+      <c r="G119" t="n">
+        <v>81.52970000000001</v>
+      </c>
+      <c r="H119" t="n">
+        <v>235.6789</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>123</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','2')</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>0.9629</v>
+      </c>
+      <c r="F120" t="n">
+        <v>1.5254</v>
+      </c>
+      <c r="G120" t="n">
+        <v>108.3928</v>
+      </c>
+      <c r="H120" t="n">
+        <v>255.3669</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>124</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','3')</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>0.9629</v>
+      </c>
+      <c r="F121" t="n">
+        <v>1.5254</v>
+      </c>
+      <c r="G121" t="n">
+        <v>108.3928</v>
+      </c>
+      <c r="H121" t="n">
+        <v>255.3669</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>125</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','2'), list('sder',c(1,3,15))</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>0.976</v>
+      </c>
+      <c r="F122" t="n">
+        <v>1.3874</v>
+      </c>
+      <c r="G122" t="n">
+        <v>89.3669</v>
+      </c>
+      <c r="H122" t="n">
+        <v>219.2825</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>126</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','2'), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>0.9817</v>
+      </c>
+      <c r="F123" t="n">
+        <v>1.4477</v>
+      </c>
+      <c r="G123" t="n">
+        <v>81.0861</v>
+      </c>
+      <c r="H123" t="n">
+        <v>235.7436</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>127</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','3'), list('sder',c(2,4,31))</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>0.9762</v>
+      </c>
+      <c r="F124" t="n">
+        <v>1.4428</v>
+      </c>
+      <c r="G124" t="n">
+        <v>91.2178</v>
+      </c>
+      <c r="H124" t="n">
+        <v>234.4268</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>172</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>list('snv',''),list('sder',c(1,3,9)),list('red',c(10,10,1))</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>0.9722</v>
+      </c>
+      <c r="F125" t="n">
+        <v>1.4296</v>
+      </c>
+      <c r="G125" t="n">
+        <v>95.24509999999999</v>
+      </c>
+      <c r="H125" t="n">
+        <v>230.9199</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>173</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(2,4,21)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>0.9808</v>
+      </c>
+      <c r="F126" t="n">
+        <v>1.5136</v>
+      </c>
+      <c r="G126" t="n">
+        <v>87.9058</v>
+      </c>
+      <c r="H126" t="n">
+        <v>252.4807</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>trans.alpha.carotene</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>174</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','3'), list('sder',c(2,4,25))</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>0.9826</v>
+      </c>
+      <c r="F127" t="n">
+        <v>1.4435</v>
+      </c>
+      <c r="G127" t="n">
+        <v>80.3111</v>
+      </c>
+      <c r="H127" t="n">
+        <v>234.6159</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_frais/trans.alpha.carotene/RANDOMSEARCH_DETAILS_trans.alpha.carotene.xlsx
+++ b/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_frais/trans.alpha.carotene/RANDOMSEARCH_DETAILS_trans.alpha.carotene.xlsx
@@ -474,20 +474,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.9723000000000001</v>
+        <v>0.9728</v>
       </c>
       <c r="F2" t="n">
-        <v>1.424</v>
+        <v>0.4948</v>
       </c>
       <c r="G2" t="n">
-        <v>93.3627</v>
+        <v>93.86409999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>229.4133</v>
+        <v>250.3525</v>
       </c>
     </row>
     <row r="3">
@@ -506,20 +506,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.9839</v>
+        <v>0.9453</v>
       </c>
       <c r="F3" t="n">
-        <v>1.4597</v>
+        <v>0.4818</v>
       </c>
       <c r="G3" t="n">
-        <v>85.8604</v>
+        <v>136.273</v>
       </c>
       <c r="H3" t="n">
-        <v>238.8598</v>
+        <v>253.5695</v>
       </c>
     </row>
     <row r="4">
@@ -542,16 +542,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.9772999999999999</v>
+        <v>0.9749</v>
       </c>
       <c r="F4" t="n">
-        <v>1.5416</v>
+        <v>0.4816</v>
       </c>
       <c r="G4" t="n">
-        <v>92.4495</v>
+        <v>97.8613</v>
       </c>
       <c r="H4" t="n">
-        <v>259.2781</v>
+        <v>253.6099</v>
       </c>
     </row>
     <row r="5">
@@ -574,16 +574,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.7649</v>
+        <v>0.7677</v>
       </c>
       <c r="F5" t="n">
-        <v>2.0661</v>
+        <v>-0.0969</v>
       </c>
       <c r="G5" t="n">
-        <v>252.8296</v>
+        <v>259.2634</v>
       </c>
       <c r="H5" t="n">
-        <v>363.7639</v>
+        <v>368.9057</v>
       </c>
     </row>
     <row r="6">
@@ -606,16 +606,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.7641</v>
+        <v>0.7749</v>
       </c>
       <c r="F6" t="n">
-        <v>2.063</v>
+        <v>-0.1095</v>
       </c>
       <c r="G6" t="n">
-        <v>252.422</v>
+        <v>256.7033</v>
       </c>
       <c r="H6" t="n">
-        <v>363.238</v>
+        <v>371.0108</v>
       </c>
     </row>
     <row r="7">
@@ -634,20 +634,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.9097</v>
+        <v>0.918</v>
       </c>
       <c r="F7" t="n">
-        <v>1.5661</v>
+        <v>0.3618</v>
       </c>
       <c r="G7" t="n">
-        <v>156.6865</v>
+        <v>150.301</v>
       </c>
       <c r="H7" t="n">
-        <v>265.0811</v>
+        <v>281.3991</v>
       </c>
     </row>
     <row r="8">
@@ -666,20 +666,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.9223</v>
+        <v>0.9109</v>
       </c>
       <c r="F8" t="n">
-        <v>1.4722</v>
+        <v>0.493</v>
       </c>
       <c r="G8" t="n">
-        <v>141.1424</v>
+        <v>149.5535</v>
       </c>
       <c r="H8" t="n">
-        <v>242.0917</v>
+        <v>250.8119</v>
       </c>
     </row>
     <row r="9">
@@ -698,20 +698,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.9756</v>
+        <v>0.9755</v>
       </c>
       <c r="F9" t="n">
-        <v>1.4439</v>
+        <v>0.5221</v>
       </c>
       <c r="G9" t="n">
-        <v>92.2286</v>
+        <v>100.8847</v>
       </c>
       <c r="H9" t="n">
-        <v>234.7231</v>
+        <v>243.4968</v>
       </c>
     </row>
     <row r="10">
@@ -730,20 +730,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.917</v>
+        <v>0.9011</v>
       </c>
       <c r="F10" t="n">
-        <v>1.5031</v>
+        <v>0.4678</v>
       </c>
       <c r="G10" t="n">
-        <v>146.6993</v>
+        <v>157.6881</v>
       </c>
       <c r="H10" t="n">
-        <v>249.8867</v>
+        <v>256.9586</v>
       </c>
     </row>
     <row r="11">
@@ -762,20 +762,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.9135</v>
+        <v>0.8983</v>
       </c>
       <c r="F11" t="n">
-        <v>1.5126</v>
+        <v>0.473</v>
       </c>
       <c r="G11" t="n">
-        <v>149.1506</v>
+        <v>159.5045</v>
       </c>
       <c r="H11" t="n">
-        <v>252.2352</v>
+        <v>255.7137</v>
       </c>
     </row>
     <row r="12">
@@ -794,20 +794,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.9127</v>
+        <v>0.8986</v>
       </c>
       <c r="F12" t="n">
-        <v>1.5119</v>
+        <v>0.4727</v>
       </c>
       <c r="G12" t="n">
-        <v>149.7073</v>
+        <v>159.3549</v>
       </c>
       <c r="H12" t="n">
-        <v>252.0566</v>
+        <v>255.7721</v>
       </c>
     </row>
     <row r="13">
@@ -826,20 +826,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.9126</v>
+        <v>0.9382</v>
       </c>
       <c r="F13" t="n">
-        <v>1.5164</v>
+        <v>0.4746</v>
       </c>
       <c r="G13" t="n">
-        <v>149.7724</v>
+        <v>128.0945</v>
       </c>
       <c r="H13" t="n">
-        <v>253.1749</v>
+        <v>255.3214</v>
       </c>
     </row>
     <row r="14">
@@ -858,20 +858,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.9137</v>
+        <v>0.8979</v>
       </c>
       <c r="F14" t="n">
-        <v>1.5072</v>
+        <v>0.4759</v>
       </c>
       <c r="G14" t="n">
-        <v>148.7983</v>
+        <v>159.7434</v>
       </c>
       <c r="H14" t="n">
-        <v>250.9189</v>
+        <v>254.9999</v>
       </c>
     </row>
     <row r="15">
@@ -890,20 +890,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.9133</v>
+        <v>0.9001</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5054</v>
+        <v>0.4713</v>
       </c>
       <c r="G15" t="n">
-        <v>148.9218</v>
+        <v>158.4136</v>
       </c>
       <c r="H15" t="n">
-        <v>250.4531</v>
+        <v>256.1081</v>
       </c>
     </row>
     <row r="16">
@@ -922,20 +922,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.9103</v>
+        <v>0.8984</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5155</v>
+        <v>0.461</v>
       </c>
       <c r="G16" t="n">
-        <v>151.0303</v>
+        <v>159.4393</v>
       </c>
       <c r="H16" t="n">
-        <v>252.9523</v>
+        <v>258.5951</v>
       </c>
     </row>
     <row r="17">
@@ -954,20 +954,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.9107</v>
+        <v>0.8971</v>
       </c>
       <c r="F17" t="n">
-        <v>1.5178</v>
+        <v>0.4646</v>
       </c>
       <c r="G17" t="n">
-        <v>150.8909</v>
+        <v>160.5754</v>
       </c>
       <c r="H17" t="n">
-        <v>253.5076</v>
+        <v>257.7243</v>
       </c>
     </row>
     <row r="18">
@@ -986,20 +986,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.9813</v>
+        <v>0.961</v>
       </c>
       <c r="F18" t="n">
-        <v>1.4402</v>
+        <v>0.5207000000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>81.17189999999999</v>
+        <v>107.1279</v>
       </c>
       <c r="H18" t="n">
-        <v>233.7493</v>
+        <v>243.851</v>
       </c>
     </row>
     <row r="19">
@@ -1018,20 +1018,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.9684</v>
+        <v>0.9629</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4273</v>
+        <v>0.5233</v>
       </c>
       <c r="G19" t="n">
-        <v>96.0209</v>
+        <v>107.9869</v>
       </c>
       <c r="H19" t="n">
-        <v>230.3034</v>
+        <v>243.2055</v>
       </c>
     </row>
     <row r="20">
@@ -1050,20 +1050,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.9739</v>
+        <v>0.9591</v>
       </c>
       <c r="F20" t="n">
-        <v>1.4162</v>
+        <v>0.5302</v>
       </c>
       <c r="G20" t="n">
-        <v>91.98269999999999</v>
+        <v>114.553</v>
       </c>
       <c r="H20" t="n">
-        <v>227.2931</v>
+        <v>241.4211</v>
       </c>
     </row>
     <row r="21">
@@ -1082,20 +1082,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.9762999999999999</v>
+        <v>0.9809</v>
       </c>
       <c r="F21" t="n">
-        <v>1.3556</v>
+        <v>0.5823</v>
       </c>
       <c r="G21" t="n">
-        <v>86.7055</v>
+        <v>81.5754</v>
       </c>
       <c r="H21" t="n">
-        <v>210.0918</v>
+        <v>227.6538</v>
       </c>
     </row>
     <row r="22">
@@ -1114,20 +1114,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.9814000000000001</v>
+        <v>0.9832</v>
       </c>
       <c r="F22" t="n">
-        <v>1.282</v>
+        <v>0.6818</v>
       </c>
       <c r="G22" t="n">
-        <v>76.39700000000001</v>
+        <v>72.0565</v>
       </c>
       <c r="H22" t="n">
-        <v>187.1045</v>
+        <v>198.7043</v>
       </c>
     </row>
     <row r="23">
@@ -1146,20 +1146,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.9855</v>
+        <v>0.9726</v>
       </c>
       <c r="F23" t="n">
-        <v>1.2989</v>
+        <v>0.6264</v>
       </c>
       <c r="G23" t="n">
-        <v>67.52809999999999</v>
+        <v>89.3485</v>
       </c>
       <c r="H23" t="n">
-        <v>192.6161</v>
+        <v>215.2891</v>
       </c>
     </row>
     <row r="24">
@@ -1178,20 +1178,20 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.9788</v>
+        <v>0.9797</v>
       </c>
       <c r="F24" t="n">
-        <v>1.3145</v>
+        <v>0.6346000000000001</v>
       </c>
       <c r="G24" t="n">
-        <v>79.3497</v>
+        <v>79.4277</v>
       </c>
       <c r="H24" t="n">
-        <v>197.5888</v>
+        <v>212.9336</v>
       </c>
     </row>
     <row r="25">
@@ -1210,20 +1210,20 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.974</v>
+        <v>0.9785</v>
       </c>
       <c r="F25" t="n">
-        <v>1.3615</v>
+        <v>0.5518999999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>85.99809999999999</v>
+        <v>84.584</v>
       </c>
       <c r="H25" t="n">
-        <v>211.818</v>
+        <v>235.7759</v>
       </c>
     </row>
     <row r="26">
@@ -1242,20 +1242,20 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.971</v>
+        <v>0.9637</v>
       </c>
       <c r="F26" t="n">
-        <v>1.4295</v>
+        <v>0.4932</v>
       </c>
       <c r="G26" t="n">
-        <v>94.483</v>
+        <v>103.7794</v>
       </c>
       <c r="H26" t="n">
-        <v>230.8981</v>
+        <v>250.7599</v>
       </c>
     </row>
     <row r="27">
@@ -1274,20 +1274,20 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.9798</v>
+        <v>0.9677</v>
       </c>
       <c r="F27" t="n">
-        <v>1.4437</v>
+        <v>0.509</v>
       </c>
       <c r="G27" t="n">
-        <v>83.46599999999999</v>
+        <v>104.6044</v>
       </c>
       <c r="H27" t="n">
-        <v>234.6887</v>
+        <v>246.8049</v>
       </c>
     </row>
     <row r="28">
@@ -1306,20 +1306,20 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.9734</v>
+        <v>0.9328</v>
       </c>
       <c r="F28" t="n">
-        <v>1.4344</v>
+        <v>0.51</v>
       </c>
       <c r="G28" t="n">
-        <v>90.9182</v>
+        <v>140.6575</v>
       </c>
       <c r="H28" t="n">
-        <v>232.1916</v>
+        <v>246.5701</v>
       </c>
     </row>
     <row r="29">
@@ -1338,20 +1338,20 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.9738</v>
+        <v>0.9721</v>
       </c>
       <c r="F29" t="n">
-        <v>1.4451</v>
+        <v>0.5319</v>
       </c>
       <c r="G29" t="n">
-        <v>91.7435</v>
+        <v>94.6078</v>
       </c>
       <c r="H29" t="n">
-        <v>235.0398</v>
+        <v>240.994</v>
       </c>
     </row>
     <row r="30">
@@ -1370,20 +1370,20 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.9754</v>
+        <v>0.9362</v>
       </c>
       <c r="F30" t="n">
-        <v>1.4072</v>
+        <v>0.5375</v>
       </c>
       <c r="G30" t="n">
-        <v>88.8998</v>
+        <v>135.5583</v>
       </c>
       <c r="H30" t="n">
-        <v>224.804</v>
+        <v>239.5421</v>
       </c>
     </row>
     <row r="31">
@@ -1406,16 +1406,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.9772</v>
+        <v>0.9751</v>
       </c>
       <c r="F31" t="n">
-        <v>1.3694</v>
+        <v>0.5878</v>
       </c>
       <c r="G31" t="n">
-        <v>86.0838</v>
+        <v>89.0772</v>
       </c>
       <c r="H31" t="n">
-        <v>214.1133</v>
+        <v>226.1318</v>
       </c>
     </row>
     <row r="32">
@@ -1438,16 +1438,16 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.9774</v>
+        <v>0.9771</v>
       </c>
       <c r="F32" t="n">
-        <v>1.3439</v>
+        <v>0.6065</v>
       </c>
       <c r="G32" t="n">
-        <v>84.58069999999999</v>
+        <v>84.51649999999999</v>
       </c>
       <c r="H32" t="n">
-        <v>206.6036</v>
+        <v>220.9673</v>
       </c>
     </row>
     <row r="33">
@@ -1466,20 +1466,20 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.9778</v>
+        <v>0.984</v>
       </c>
       <c r="F33" t="n">
-        <v>1.3457</v>
+        <v>0.6342</v>
       </c>
       <c r="G33" t="n">
-        <v>84.0839</v>
+        <v>72.88760000000001</v>
       </c>
       <c r="H33" t="n">
-        <v>207.1352</v>
+        <v>213.0256</v>
       </c>
     </row>
     <row r="34">
@@ -1498,20 +1498,20 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.9739</v>
+        <v>0.9698</v>
       </c>
       <c r="F34" t="n">
-        <v>1.516</v>
+        <v>0.4389</v>
       </c>
       <c r="G34" t="n">
-        <v>98.425</v>
+        <v>106.3691</v>
       </c>
       <c r="H34" t="n">
-        <v>253.0774</v>
+        <v>263.8356</v>
       </c>
     </row>
     <row r="35">
@@ -1530,20 +1530,20 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.9727</v>
+        <v>0.9815</v>
       </c>
       <c r="F35" t="n">
-        <v>1.4987</v>
+        <v>0.4735</v>
       </c>
       <c r="G35" t="n">
-        <v>103.4145</v>
+        <v>92.09439999999999</v>
       </c>
       <c r="H35" t="n">
-        <v>248.7952</v>
+        <v>255.5907</v>
       </c>
     </row>
     <row r="36">
@@ -1562,20 +1562,20 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.977</v>
+        <v>0.9811</v>
       </c>
       <c r="F36" t="n">
-        <v>1.4535</v>
+        <v>0.4962</v>
       </c>
       <c r="G36" t="n">
-        <v>91.57810000000001</v>
+        <v>92.8693</v>
       </c>
       <c r="H36" t="n">
-        <v>237.2451</v>
+        <v>250.0123</v>
       </c>
     </row>
     <row r="37">
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.9742</v>
+        <v>0.9716</v>
       </c>
       <c r="F37" t="n">
-        <v>1.4271</v>
+        <v>0.5165</v>
       </c>
       <c r="G37" t="n">
-        <v>94.56</v>
+        <v>100.8629</v>
       </c>
       <c r="H37" t="n">
-        <v>230.2553</v>
+        <v>244.9195</v>
       </c>
     </row>
     <row r="38">
@@ -1626,20 +1626,20 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.982</v>
+        <v>0.9776</v>
       </c>
       <c r="F38" t="n">
-        <v>1.4214</v>
+        <v>0.5367</v>
       </c>
       <c r="G38" t="n">
-        <v>80.5214</v>
+        <v>92.7641</v>
       </c>
       <c r="H38" t="n">
-        <v>228.6918</v>
+        <v>239.7502</v>
       </c>
     </row>
     <row r="39">
@@ -1662,16 +1662,16 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.9749</v>
+        <v>0.9671</v>
       </c>
       <c r="F39" t="n">
-        <v>1.4162</v>
+        <v>0.5439000000000001</v>
       </c>
       <c r="G39" t="n">
-        <v>90.28270000000001</v>
+        <v>104.0797</v>
       </c>
       <c r="H39" t="n">
-        <v>227.2819</v>
+        <v>237.8769</v>
       </c>
     </row>
     <row r="40">
@@ -1690,20 +1690,20 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.9818</v>
+        <v>0.9321</v>
       </c>
       <c r="F40" t="n">
-        <v>1.4221</v>
+        <v>0.5407</v>
       </c>
       <c r="G40" t="n">
-        <v>77.70950000000001</v>
+        <v>139.3589</v>
       </c>
       <c r="H40" t="n">
-        <v>228.8873</v>
+        <v>238.7088</v>
       </c>
     </row>
     <row r="41">
@@ -1722,20 +1722,20 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.9834000000000001</v>
+        <v>0.9699</v>
       </c>
       <c r="F41" t="n">
-        <v>1.5183</v>
+        <v>0.438</v>
       </c>
       <c r="G41" t="n">
-        <v>88.16759999999999</v>
+        <v>106.1345</v>
       </c>
       <c r="H41" t="n">
-        <v>253.6345</v>
+        <v>264.0687</v>
       </c>
     </row>
     <row r="42">
@@ -1754,20 +1754,20 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.974</v>
+        <v>0.9821</v>
       </c>
       <c r="F42" t="n">
-        <v>1.4967</v>
+        <v>0.4717</v>
       </c>
       <c r="G42" t="n">
-        <v>97.77070000000001</v>
+        <v>91.5424</v>
       </c>
       <c r="H42" t="n">
-        <v>248.3072</v>
+        <v>256.0155</v>
       </c>
     </row>
     <row r="43">
@@ -1786,20 +1786,20 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.977</v>
+        <v>0.9794</v>
       </c>
       <c r="F43" t="n">
-        <v>1.4538</v>
+        <v>0.5027</v>
       </c>
       <c r="G43" t="n">
-        <v>91.7924</v>
+        <v>94.02070000000001</v>
       </c>
       <c r="H43" t="n">
-        <v>237.341</v>
+        <v>248.4042</v>
       </c>
     </row>
     <row r="44">
@@ -1822,16 +1822,16 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.9743000000000001</v>
+        <v>0.9721</v>
       </c>
       <c r="F44" t="n">
-        <v>1.423</v>
+        <v>0.5219</v>
       </c>
       <c r="G44" t="n">
-        <v>93.946</v>
+        <v>100.3852</v>
       </c>
       <c r="H44" t="n">
-        <v>229.1359</v>
+        <v>243.5513</v>
       </c>
     </row>
     <row r="45">
@@ -1850,20 +1850,20 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.9819</v>
+        <v>0.9772999999999999</v>
       </c>
       <c r="F45" t="n">
-        <v>1.4187</v>
+        <v>0.5395</v>
       </c>
       <c r="G45" t="n">
-        <v>80.681</v>
+        <v>92.12569999999999</v>
       </c>
       <c r="H45" t="n">
-        <v>227.9688</v>
+        <v>239.0226</v>
       </c>
     </row>
     <row r="46">
@@ -1886,16 +1886,16 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.9736</v>
+        <v>0.9663</v>
       </c>
       <c r="F46" t="n">
-        <v>1.4275</v>
+        <v>0.5464</v>
       </c>
       <c r="G46" t="n">
-        <v>92.1026</v>
+        <v>105.1776</v>
       </c>
       <c r="H46" t="n">
-        <v>230.3525</v>
+        <v>237.2232</v>
       </c>
     </row>
     <row r="47">
@@ -1914,20 +1914,20 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.9826</v>
+        <v>0.9327</v>
       </c>
       <c r="F47" t="n">
-        <v>1.435</v>
+        <v>0.5331</v>
       </c>
       <c r="G47" t="n">
-        <v>76.8366</v>
+        <v>139.2286</v>
       </c>
       <c r="H47" t="n">
-        <v>232.3625</v>
+        <v>240.6827</v>
       </c>
     </row>
     <row r="48">
@@ -1946,20 +1946,20 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.9752</v>
+        <v>0.9792</v>
       </c>
       <c r="F48" t="n">
-        <v>1.4727</v>
+        <v>0.5004999999999999</v>
       </c>
       <c r="G48" t="n">
-        <v>94.1597</v>
+        <v>94.2423</v>
       </c>
       <c r="H48" t="n">
-        <v>242.2113</v>
+        <v>248.9457</v>
       </c>
     </row>
     <row r="49">
@@ -1978,20 +1978,20 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.9761</v>
+        <v>0.9812</v>
       </c>
       <c r="F49" t="n">
-        <v>1.4473</v>
+        <v>0.4979</v>
       </c>
       <c r="G49" t="n">
-        <v>92.15089999999999</v>
+        <v>94.2527</v>
       </c>
       <c r="H49" t="n">
-        <v>235.635</v>
+        <v>249.5918</v>
       </c>
     </row>
     <row r="50">
@@ -2010,20 +2010,20 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.9119</v>
+        <v>0.9044</v>
       </c>
       <c r="F50" t="n">
-        <v>1.9523</v>
+        <v>0.0048</v>
       </c>
       <c r="G50" t="n">
-        <v>209.3237</v>
+        <v>225.1703</v>
       </c>
       <c r="H50" t="n">
-        <v>343.8104</v>
+        <v>351.3875</v>
       </c>
     </row>
     <row r="51">
@@ -2042,20 +2042,20 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.877</v>
+        <v>0.8678</v>
       </c>
       <c r="F51" t="n">
-        <v>1.9372</v>
+        <v>-0.0143</v>
       </c>
       <c r="G51" t="n">
-        <v>214.556</v>
+        <v>235.8679</v>
       </c>
       <c r="H51" t="n">
-        <v>341.0743</v>
+        <v>354.7495</v>
       </c>
     </row>
     <row r="52">
@@ -2078,16 +2078,16 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.8506</v>
+        <v>0.8641</v>
       </c>
       <c r="F52" t="n">
-        <v>1.9508</v>
+        <v>-0.0098</v>
       </c>
       <c r="G52" t="n">
-        <v>233.4296</v>
+        <v>236.6275</v>
       </c>
       <c r="H52" t="n">
-        <v>343.5357</v>
+        <v>353.9571</v>
       </c>
     </row>
     <row r="53">
@@ -2106,20 +2106,20 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.9021</v>
+        <v>0.9157999999999999</v>
       </c>
       <c r="F53" t="n">
-        <v>1.9178</v>
+        <v>0.0449</v>
       </c>
       <c r="G53" t="n">
-        <v>213.8773</v>
+        <v>206.3964</v>
       </c>
       <c r="H53" t="n">
-        <v>337.5124</v>
+        <v>344.2425</v>
       </c>
     </row>
     <row r="54">
@@ -2138,20 +2138,20 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.9097</v>
+        <v>0.9028</v>
       </c>
       <c r="F54" t="n">
-        <v>1.924</v>
+        <v>0.025</v>
       </c>
       <c r="G54" t="n">
-        <v>202.1652</v>
+        <v>223.2093</v>
       </c>
       <c r="H54" t="n">
-        <v>338.6537</v>
+        <v>347.797</v>
       </c>
     </row>
     <row r="55">
@@ -2170,20 +2170,20 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.9082</v>
+        <v>0.9101</v>
       </c>
       <c r="F55" t="n">
-        <v>1.9726</v>
+        <v>-0.0298</v>
       </c>
       <c r="G55" t="n">
-        <v>207.6191</v>
+        <v>223.3884</v>
       </c>
       <c r="H55" t="n">
-        <v>347.4456</v>
+        <v>357.4415</v>
       </c>
     </row>
     <row r="56">
@@ -2202,20 +2202,20 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.9326</v>
+        <v>0.9107</v>
       </c>
       <c r="F56" t="n">
-        <v>1.9764</v>
+        <v>-0.0121</v>
       </c>
       <c r="G56" t="n">
-        <v>211.907</v>
+        <v>230.7422</v>
       </c>
       <c r="H56" t="n">
-        <v>348.1214</v>
+        <v>354.3518</v>
       </c>
     </row>
     <row r="57">
@@ -2234,20 +2234,20 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.8956</v>
+        <v>0.9155</v>
       </c>
       <c r="F57" t="n">
-        <v>1.9988</v>
+        <v>-0.0249</v>
       </c>
       <c r="G57" t="n">
-        <v>226.0602</v>
+        <v>221.7532</v>
       </c>
       <c r="H57" t="n">
-        <v>352.0956</v>
+        <v>356.5844</v>
       </c>
     </row>
     <row r="58">
@@ -2270,16 +2270,16 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.7635</v>
+        <v>0.7761</v>
       </c>
       <c r="F58" t="n">
-        <v>2.0608</v>
+        <v>-0.1055</v>
       </c>
       <c r="G58" t="n">
-        <v>252.5761</v>
+        <v>256.2382</v>
       </c>
       <c r="H58" t="n">
-        <v>362.8539</v>
+        <v>370.3447</v>
       </c>
     </row>
     <row r="59">
@@ -2302,16 +2302,16 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.7641</v>
+        <v>0.7741</v>
       </c>
       <c r="F59" t="n">
-        <v>2.0563</v>
+        <v>-0.1049</v>
       </c>
       <c r="G59" t="n">
-        <v>252.5934</v>
+        <v>256.8093</v>
       </c>
       <c r="H59" t="n">
-        <v>362.0933</v>
+        <v>370.2402</v>
       </c>
     </row>
     <row r="60">
@@ -2334,16 +2334,16 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.7627</v>
+        <v>0.7741</v>
       </c>
       <c r="F60" t="n">
-        <v>2.0567</v>
+        <v>-0.1062</v>
       </c>
       <c r="G60" t="n">
-        <v>252.9306</v>
+        <v>256.6692</v>
       </c>
       <c r="H60" t="n">
-        <v>362.1641</v>
+        <v>370.4587</v>
       </c>
     </row>
     <row r="61">
@@ -2366,16 +2366,16 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.7634</v>
+        <v>0.7746</v>
       </c>
       <c r="F61" t="n">
-        <v>2.059</v>
+        <v>-0.105</v>
       </c>
       <c r="G61" t="n">
-        <v>252.8199</v>
+        <v>256.8933</v>
       </c>
       <c r="H61" t="n">
-        <v>362.5456</v>
+        <v>370.2625</v>
       </c>
     </row>
     <row r="62">
@@ -2398,16 +2398,16 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.8351</v>
+        <v>0.8482</v>
       </c>
       <c r="F62" t="n">
-        <v>2.0334</v>
+        <v>-0.0336</v>
       </c>
       <c r="G62" t="n">
-        <v>236.5533</v>
+        <v>243.8423</v>
       </c>
       <c r="H62" t="n">
-        <v>358.1365</v>
+        <v>358.1022</v>
       </c>
     </row>
     <row r="63">
@@ -2430,16 +2430,16 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.8286</v>
+        <v>0.8493000000000001</v>
       </c>
       <c r="F63" t="n">
-        <v>2.0251</v>
+        <v>-0.0213</v>
       </c>
       <c r="G63" t="n">
-        <v>237.5554</v>
+        <v>242.9915</v>
       </c>
       <c r="H63" t="n">
-        <v>356.6978</v>
+        <v>355.9616</v>
       </c>
     </row>
     <row r="64">
@@ -2462,16 +2462,16 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.8222</v>
+        <v>0.8317</v>
       </c>
       <c r="F64" t="n">
-        <v>2.0324</v>
+        <v>-0.0164</v>
       </c>
       <c r="G64" t="n">
-        <v>236.9788</v>
+        <v>245.2846</v>
       </c>
       <c r="H64" t="n">
-        <v>357.9793</v>
+        <v>355.1168</v>
       </c>
     </row>
     <row r="65">
@@ -2494,16 +2494,16 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.8118</v>
+        <v>0.822</v>
       </c>
       <c r="F65" t="n">
-        <v>2.0308</v>
+        <v>-0.0259</v>
       </c>
       <c r="G65" t="n">
-        <v>238.2407</v>
+        <v>246.5265</v>
       </c>
       <c r="H65" t="n">
-        <v>357.6918</v>
+        <v>356.7583</v>
       </c>
     </row>
     <row r="66">
@@ -2526,16 +2526,16 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.8927</v>
+        <v>0.8991</v>
       </c>
       <c r="F66" t="n">
-        <v>2.0028</v>
+        <v>-0.0162</v>
       </c>
       <c r="G66" t="n">
-        <v>226.1244</v>
+        <v>232.3784</v>
       </c>
       <c r="H66" t="n">
-        <v>352.7958</v>
+        <v>355.0701</v>
       </c>
     </row>
     <row r="67">
@@ -2554,20 +2554,20 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.9082</v>
+        <v>0.898</v>
       </c>
       <c r="F67" t="n">
-        <v>1.9844</v>
+        <v>0.007</v>
       </c>
       <c r="G67" t="n">
-        <v>214.4214</v>
+        <v>228.8217</v>
       </c>
       <c r="H67" t="n">
-        <v>349.5519</v>
+        <v>351.0011</v>
       </c>
     </row>
     <row r="68">
@@ -2586,20 +2586,20 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.9102</v>
+        <v>0.8986</v>
       </c>
       <c r="F68" t="n">
-        <v>1.993</v>
+        <v>-0.016</v>
       </c>
       <c r="G68" t="n">
-        <v>213.4904</v>
+        <v>230.5474</v>
       </c>
       <c r="H68" t="n">
-        <v>351.0813</v>
+        <v>355.038</v>
       </c>
     </row>
     <row r="69">
@@ -2618,20 +2618,20 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E69" t="n">
         <v>0.9792</v>
       </c>
       <c r="F69" t="n">
-        <v>1.3479</v>
+        <v>0.6335</v>
       </c>
       <c r="G69" t="n">
-        <v>82.7591</v>
+        <v>85.3488</v>
       </c>
       <c r="H69" t="n">
-        <v>207.8076</v>
+        <v>213.2302</v>
       </c>
     </row>
     <row r="70">
@@ -2654,16 +2654,16 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.9831</v>
+        <v>0.9821</v>
       </c>
       <c r="F70" t="n">
-        <v>1.324</v>
+        <v>0.655</v>
       </c>
       <c r="G70" t="n">
-        <v>72.82729999999999</v>
+        <v>74.3676</v>
       </c>
       <c r="H70" t="n">
-        <v>200.5311</v>
+        <v>206.9049</v>
       </c>
     </row>
     <row r="71">
@@ -2682,20 +2682,20 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.975</v>
+        <v>0.9505</v>
       </c>
       <c r="F71" t="n">
-        <v>1.3908</v>
+        <v>0.5498</v>
       </c>
       <c r="G71" t="n">
-        <v>90.1444</v>
+        <v>121.1624</v>
       </c>
       <c r="H71" t="n">
-        <v>220.241</v>
+        <v>236.332</v>
       </c>
     </row>
     <row r="72">
@@ -2714,20 +2714,20 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.9827</v>
+        <v>0.9749</v>
       </c>
       <c r="F72" t="n">
-        <v>1.3634</v>
+        <v>0.5756</v>
       </c>
       <c r="G72" t="n">
-        <v>76.25700000000001</v>
+        <v>90.0421</v>
       </c>
       <c r="H72" t="n">
-        <v>212.3687</v>
+        <v>229.4728</v>
       </c>
     </row>
     <row r="73">
@@ -2750,16 +2750,16 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.982</v>
+        <v>0.9774</v>
       </c>
       <c r="F73" t="n">
-        <v>1.4836</v>
+        <v>0.451</v>
       </c>
       <c r="G73" t="n">
-        <v>84.96420000000001</v>
+        <v>94.4307</v>
       </c>
       <c r="H73" t="n">
-        <v>245.0072</v>
+        <v>260.9749</v>
       </c>
     </row>
     <row r="74">
@@ -2778,20 +2778,20 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.9721</v>
+        <v>0.9678</v>
       </c>
       <c r="F74" t="n">
-        <v>1.4357</v>
+        <v>0.4944</v>
       </c>
       <c r="G74" t="n">
-        <v>97.7123</v>
+        <v>102.7229</v>
       </c>
       <c r="H74" t="n">
-        <v>232.551</v>
+        <v>250.4497</v>
       </c>
     </row>
     <row r="75">
@@ -2810,20 +2810,20 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.9201</v>
+        <v>0.9564</v>
       </c>
       <c r="F75" t="n">
-        <v>1.5616</v>
+        <v>0.3876</v>
       </c>
       <c r="G75" t="n">
-        <v>147.7631</v>
+        <v>116.5412</v>
       </c>
       <c r="H75" t="n">
-        <v>264.0132</v>
+        <v>275.638</v>
       </c>
     </row>
     <row r="76">
@@ -2842,20 +2842,20 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.9201</v>
+        <v>0.9564</v>
       </c>
       <c r="F76" t="n">
-        <v>1.5616</v>
+        <v>0.3876</v>
       </c>
       <c r="G76" t="n">
-        <v>147.7631</v>
+        <v>116.5412</v>
       </c>
       <c r="H76" t="n">
-        <v>264.0132</v>
+        <v>275.638</v>
       </c>
     </row>
     <row r="77">
@@ -2874,20 +2874,20 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.8270999999999999</v>
+        <v>0.8588</v>
       </c>
       <c r="F77" t="n">
-        <v>2.0458</v>
+        <v>-0.1004</v>
       </c>
       <c r="G77" t="n">
-        <v>228.0066</v>
+        <v>227.148</v>
       </c>
       <c r="H77" t="n">
-        <v>360.2827</v>
+        <v>369.4907</v>
       </c>
     </row>
     <row r="78">
@@ -2906,20 +2906,20 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.8275</v>
+        <v>0.8596</v>
       </c>
       <c r="F78" t="n">
-        <v>2.0549</v>
+        <v>-0.09279999999999999</v>
       </c>
       <c r="G78" t="n">
-        <v>228.6252</v>
+        <v>228.1713</v>
       </c>
       <c r="H78" t="n">
-        <v>361.8529</v>
+        <v>368.2083</v>
       </c>
     </row>
     <row r="79">
@@ -2938,20 +2938,20 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.8275</v>
+        <v>0.8573</v>
       </c>
       <c r="F79" t="n">
-        <v>2.0552</v>
+        <v>-0.0954</v>
       </c>
       <c r="G79" t="n">
-        <v>229.0747</v>
+        <v>228.5671</v>
       </c>
       <c r="H79" t="n">
-        <v>361.9083</v>
+        <v>368.659</v>
       </c>
     </row>
     <row r="80">
@@ -2970,20 +2970,20 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.8267</v>
+        <v>0.8598</v>
       </c>
       <c r="F80" t="n">
-        <v>2.0541</v>
+        <v>-0.0927</v>
       </c>
       <c r="G80" t="n">
-        <v>228.8719</v>
+        <v>228.1251</v>
       </c>
       <c r="H80" t="n">
-        <v>361.7198</v>
+        <v>368.1949</v>
       </c>
     </row>
     <row r="81">
@@ -3002,20 +3002,20 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.893</v>
+        <v>0.8727</v>
       </c>
       <c r="F81" t="n">
-        <v>1.9743</v>
+        <v>-0.042</v>
       </c>
       <c r="G81" t="n">
-        <v>209.4573</v>
+        <v>238.8199</v>
       </c>
       <c r="H81" t="n">
-        <v>347.7539</v>
+        <v>359.5501</v>
       </c>
     </row>
     <row r="82">
@@ -3038,16 +3038,16 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>0.8601</v>
+        <v>0.872</v>
       </c>
       <c r="F82" t="n">
-        <v>1.987</v>
+        <v>-0.0339</v>
       </c>
       <c r="G82" t="n">
-        <v>231.9082</v>
+        <v>238.3399</v>
       </c>
       <c r="H82" t="n">
-        <v>350.0103</v>
+        <v>358.1521</v>
       </c>
     </row>
     <row r="83">
@@ -3070,16 +3070,16 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.9212</v>
+        <v>0.9004</v>
       </c>
       <c r="F83" t="n">
-        <v>1.5497</v>
+        <v>0.3913</v>
       </c>
       <c r="G83" t="n">
-        <v>147.386</v>
+        <v>162.7316</v>
       </c>
       <c r="H83" t="n">
-        <v>261.2025</v>
+        <v>274.8026</v>
       </c>
     </row>
     <row r="84">
@@ -3102,16 +3102,16 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.9208</v>
+        <v>0.9004</v>
       </c>
       <c r="F84" t="n">
-        <v>1.5495</v>
+        <v>0.3923</v>
       </c>
       <c r="G84" t="n">
-        <v>147.7006</v>
+        <v>162.5962</v>
       </c>
       <c r="H84" t="n">
-        <v>261.1516</v>
+        <v>274.5953</v>
       </c>
     </row>
     <row r="85">
@@ -3134,16 +3134,16 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.9204</v>
+        <v>0.9009</v>
       </c>
       <c r="F85" t="n">
-        <v>1.5498</v>
+        <v>0.3948</v>
       </c>
       <c r="G85" t="n">
-        <v>147.9593</v>
+        <v>162.5504</v>
       </c>
       <c r="H85" t="n">
-        <v>261.2354</v>
+        <v>274.0239</v>
       </c>
     </row>
     <row r="86">
@@ -3162,20 +3162,20 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.9742</v>
+        <v>0.9457</v>
       </c>
       <c r="F86" t="n">
-        <v>1.4171</v>
+        <v>0.52</v>
       </c>
       <c r="G86" t="n">
-        <v>89.32259999999999</v>
+        <v>123.8419</v>
       </c>
       <c r="H86" t="n">
-        <v>227.5229</v>
+        <v>244.0373</v>
       </c>
     </row>
     <row r="87">
@@ -3194,20 +3194,20 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.9722</v>
+        <v>0.9616</v>
       </c>
       <c r="F87" t="n">
-        <v>1.4303</v>
+        <v>0.5181</v>
       </c>
       <c r="G87" t="n">
-        <v>93.01439999999999</v>
+        <v>106.8391</v>
       </c>
       <c r="H87" t="n">
-        <v>231.0967</v>
+        <v>244.522</v>
       </c>
     </row>
     <row r="88">
@@ -3226,20 +3226,20 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.9824000000000001</v>
+        <v>0.9439</v>
       </c>
       <c r="F88" t="n">
-        <v>1.4432</v>
+        <v>0.5231</v>
       </c>
       <c r="G88" t="n">
-        <v>77.60899999999999</v>
+        <v>127.252</v>
       </c>
       <c r="H88" t="n">
-        <v>234.5314</v>
+        <v>243.2424</v>
       </c>
     </row>
     <row r="89">
@@ -3258,20 +3258,20 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0.9811</v>
+        <v>0.9636</v>
       </c>
       <c r="F89" t="n">
-        <v>1.4196</v>
+        <v>0.541</v>
       </c>
       <c r="G89" t="n">
-        <v>78.48180000000001</v>
+        <v>105.9764</v>
       </c>
       <c r="H89" t="n">
-        <v>228.209</v>
+        <v>238.6449</v>
       </c>
     </row>
     <row r="90">
@@ -3290,20 +3290,20 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>0.9769</v>
+        <v>0.9795</v>
       </c>
       <c r="F90" t="n">
-        <v>1.454</v>
+        <v>0.5034999999999999</v>
       </c>
       <c r="G90" t="n">
-        <v>91.81699999999999</v>
+        <v>93.9179</v>
       </c>
       <c r="H90" t="n">
-        <v>237.3748</v>
+        <v>248.1965</v>
       </c>
     </row>
     <row r="91">
@@ -3326,16 +3326,16 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0.9743000000000001</v>
+        <v>0.9721</v>
       </c>
       <c r="F91" t="n">
-        <v>1.423</v>
+        <v>0.522</v>
       </c>
       <c r="G91" t="n">
-        <v>93.96639999999999</v>
+        <v>100.3852</v>
       </c>
       <c r="H91" t="n">
-        <v>229.132</v>
+        <v>243.5336</v>
       </c>
     </row>
     <row r="92">
@@ -3354,20 +3354,20 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0.9824000000000001</v>
+        <v>0.9439</v>
       </c>
       <c r="F92" t="n">
-        <v>1.4432</v>
+        <v>0.5231</v>
       </c>
       <c r="G92" t="n">
-        <v>77.60899999999999</v>
+        <v>127.252</v>
       </c>
       <c r="H92" t="n">
-        <v>234.5314</v>
+        <v>243.2424</v>
       </c>
     </row>
     <row r="93">
@@ -3390,16 +3390,16 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0.9743000000000001</v>
+        <v>0.9721</v>
       </c>
       <c r="F93" t="n">
-        <v>1.423</v>
+        <v>0.522</v>
       </c>
       <c r="G93" t="n">
-        <v>93.96639999999999</v>
+        <v>100.3852</v>
       </c>
       <c r="H93" t="n">
-        <v>229.132</v>
+        <v>243.5336</v>
       </c>
     </row>
     <row r="94">
@@ -3422,16 +3422,16 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.9772999999999999</v>
+        <v>0.9749</v>
       </c>
       <c r="F94" t="n">
-        <v>1.5416</v>
+        <v>0.4816</v>
       </c>
       <c r="G94" t="n">
-        <v>92.4495</v>
+        <v>97.8613</v>
       </c>
       <c r="H94" t="n">
-        <v>259.2781</v>
+        <v>253.6099</v>
       </c>
     </row>
     <row r="95">
@@ -3450,20 +3450,20 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.728</v>
+        <v>0.771</v>
       </c>
       <c r="F95" t="n">
-        <v>2.0595</v>
+        <v>-0.1272</v>
       </c>
       <c r="G95" t="n">
-        <v>264.4096</v>
+        <v>258.2216</v>
       </c>
       <c r="H95" t="n">
-        <v>362.632</v>
+        <v>373.9602</v>
       </c>
     </row>
     <row r="96">
@@ -3486,16 +3486,16 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.9781</v>
+        <v>0.9737</v>
       </c>
       <c r="F96" t="n">
-        <v>1.5418</v>
+        <v>0.4741</v>
       </c>
       <c r="G96" t="n">
-        <v>92.9954</v>
+        <v>99.17149999999999</v>
       </c>
       <c r="H96" t="n">
-        <v>259.3289</v>
+        <v>255.4357</v>
       </c>
     </row>
     <row r="97">
@@ -3518,16 +3518,16 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.9786</v>
+        <v>0.974</v>
       </c>
       <c r="F97" t="n">
-        <v>1.5395</v>
+        <v>0.476</v>
       </c>
       <c r="G97" t="n">
-        <v>92.209</v>
+        <v>99.1438</v>
       </c>
       <c r="H97" t="n">
-        <v>258.7726</v>
+        <v>254.9717</v>
       </c>
     </row>
     <row r="98">
@@ -3550,16 +3550,16 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.9802999999999999</v>
+        <v>0.9731</v>
       </c>
       <c r="F98" t="n">
-        <v>1.4445</v>
+        <v>0.5011</v>
       </c>
       <c r="G98" t="n">
-        <v>82.7825</v>
+        <v>96.26430000000001</v>
       </c>
       <c r="H98" t="n">
-        <v>234.8903</v>
+        <v>248.8048</v>
       </c>
     </row>
     <row r="99">
@@ -3578,20 +3578,20 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.9811</v>
+        <v>0.9792</v>
       </c>
       <c r="F99" t="n">
-        <v>1.3776</v>
+        <v>0.526</v>
       </c>
       <c r="G99" t="n">
-        <v>78.70869999999999</v>
+        <v>86.45050000000001</v>
       </c>
       <c r="H99" t="n">
-        <v>216.4851</v>
+        <v>242.5061</v>
       </c>
     </row>
     <row r="100">
@@ -3614,16 +3614,16 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.9747</v>
+        <v>0.9723000000000001</v>
       </c>
       <c r="F100" t="n">
-        <v>1.3651</v>
+        <v>0.5581</v>
       </c>
       <c r="G100" t="n">
-        <v>88.2054</v>
+        <v>91.82559999999999</v>
       </c>
       <c r="H100" t="n">
-        <v>212.8775</v>
+        <v>234.1495</v>
       </c>
     </row>
     <row r="101">
@@ -3642,20 +3642,20 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.9761</v>
+        <v>0.9785</v>
       </c>
       <c r="F101" t="n">
-        <v>1.3372</v>
+        <v>0.6508</v>
       </c>
       <c r="G101" t="n">
-        <v>84.2809</v>
+        <v>79.5399</v>
       </c>
       <c r="H101" t="n">
-        <v>204.5685</v>
+        <v>208.136</v>
       </c>
     </row>
     <row r="102">
@@ -3674,20 +3674,20 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>0.9736</v>
+        <v>0.9308</v>
       </c>
       <c r="F102" t="n">
-        <v>1.3863</v>
+        <v>0.5538999999999999</v>
       </c>
       <c r="G102" t="n">
-        <v>89.9252</v>
+        <v>134.6138</v>
       </c>
       <c r="H102" t="n">
-        <v>218.9845</v>
+        <v>235.2503</v>
       </c>
     </row>
     <row r="103">
@@ -3706,20 +3706,20 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>0.9731</v>
+        <v>0.9661999999999999</v>
       </c>
       <c r="F103" t="n">
-        <v>1.4741</v>
+        <v>0.478</v>
       </c>
       <c r="G103" t="n">
-        <v>97.0878</v>
+        <v>105.6511</v>
       </c>
       <c r="H103" t="n">
-        <v>242.5779</v>
+        <v>254.4828</v>
       </c>
     </row>
     <row r="104">
@@ -3738,20 +3738,20 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>0.9814000000000001</v>
+        <v>0.9686</v>
       </c>
       <c r="F104" t="n">
-        <v>1.4518</v>
+        <v>0.496</v>
       </c>
       <c r="G104" t="n">
-        <v>82.9134</v>
+        <v>102.4674</v>
       </c>
       <c r="H104" t="n">
-        <v>236.8091</v>
+        <v>250.0607</v>
       </c>
     </row>
     <row r="105">
@@ -3770,20 +3770,20 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>0.9826</v>
+        <v>0.9688</v>
       </c>
       <c r="F105" t="n">
-        <v>1.4345</v>
+        <v>0.5334</v>
       </c>
       <c r="G105" t="n">
-        <v>79.16240000000001</v>
+        <v>99.3232</v>
       </c>
       <c r="H105" t="n">
-        <v>232.2231</v>
+        <v>240.5919</v>
       </c>
     </row>
     <row r="106">
@@ -3802,20 +3802,20 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>0.973</v>
+        <v>0.9794</v>
       </c>
       <c r="F106" t="n">
-        <v>1.3845</v>
+        <v>0.5322</v>
       </c>
       <c r="G106" t="n">
-        <v>91.8643</v>
+        <v>86.71469999999999</v>
       </c>
       <c r="H106" t="n">
-        <v>218.4622</v>
+        <v>240.9245</v>
       </c>
     </row>
     <row r="107">
@@ -3834,20 +3834,20 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>0.9755</v>
+        <v>0.9465</v>
       </c>
       <c r="F107" t="n">
-        <v>1.36</v>
+        <v>0.6008</v>
       </c>
       <c r="G107" t="n">
-        <v>86.95910000000001</v>
+        <v>120.5981</v>
       </c>
       <c r="H107" t="n">
-        <v>211.3758</v>
+        <v>222.5427</v>
       </c>
     </row>
     <row r="108">
@@ -3866,20 +3866,20 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>0.9708</v>
+        <v>0.9491000000000001</v>
       </c>
       <c r="F108" t="n">
-        <v>1.5284</v>
+        <v>0.4504</v>
       </c>
       <c r="G108" t="n">
-        <v>102.1559</v>
+        <v>138.8285</v>
       </c>
       <c r="H108" t="n">
-        <v>256.0956</v>
+        <v>261.1318</v>
       </c>
     </row>
     <row r="109">
@@ -3898,20 +3898,20 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>0.9812</v>
+        <v>0.9702</v>
       </c>
       <c r="F109" t="n">
-        <v>1.4462</v>
+        <v>0.511</v>
       </c>
       <c r="G109" t="n">
-        <v>82.7079</v>
+        <v>102.6003</v>
       </c>
       <c r="H109" t="n">
-        <v>235.3326</v>
+        <v>246.3217</v>
       </c>
     </row>
     <row r="110">
@@ -3930,20 +3930,20 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>0.9823</v>
+        <v>0.9759</v>
       </c>
       <c r="F110" t="n">
-        <v>1.4294</v>
+        <v>0.5347</v>
       </c>
       <c r="G110" t="n">
-        <v>80.7128</v>
+        <v>95.4939</v>
       </c>
       <c r="H110" t="n">
-        <v>230.8533</v>
+        <v>240.2621</v>
       </c>
     </row>
     <row r="111">
@@ -3962,20 +3962,20 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>0.9805</v>
+        <v>0.9762999999999999</v>
       </c>
       <c r="F111" t="n">
-        <v>1.3956</v>
+        <v>0.5387</v>
       </c>
       <c r="G111" t="n">
-        <v>79.976</v>
+        <v>93.1994</v>
       </c>
       <c r="H111" t="n">
-        <v>221.5791</v>
+        <v>239.2377</v>
       </c>
     </row>
     <row r="112">
@@ -3994,20 +3994,20 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>0.9712</v>
+        <v>0.9495</v>
       </c>
       <c r="F112" t="n">
-        <v>1.527</v>
+        <v>0.452</v>
       </c>
       <c r="G112" t="n">
-        <v>101.7312</v>
+        <v>138.4463</v>
       </c>
       <c r="H112" t="n">
-        <v>255.757</v>
+        <v>260.7425</v>
       </c>
     </row>
     <row r="113">
@@ -4026,20 +4026,20 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>0.9814000000000001</v>
+        <v>0.9705</v>
       </c>
       <c r="F113" t="n">
-        <v>1.4475</v>
+        <v>0.5078</v>
       </c>
       <c r="G113" t="n">
-        <v>81.52970000000001</v>
+        <v>102.3611</v>
       </c>
       <c r="H113" t="n">
-        <v>235.6789</v>
+        <v>247.1155</v>
       </c>
     </row>
     <row r="114">
@@ -4058,20 +4058,20 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>0.9818</v>
+        <v>0.9752</v>
       </c>
       <c r="F114" t="n">
-        <v>1.4215</v>
+        <v>0.5367</v>
       </c>
       <c r="G114" t="n">
-        <v>81.01479999999999</v>
+        <v>96.4973</v>
       </c>
       <c r="H114" t="n">
-        <v>228.723</v>
+        <v>239.7573</v>
       </c>
     </row>
     <row r="115">
@@ -4090,20 +4090,20 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>0.9715</v>
+        <v>0.974</v>
       </c>
       <c r="F115" t="n">
-        <v>1.3973</v>
+        <v>0.5341</v>
       </c>
       <c r="G115" t="n">
-        <v>94.6212</v>
+        <v>95.0127</v>
       </c>
       <c r="H115" t="n">
-        <v>222.0556</v>
+        <v>240.4166</v>
       </c>
     </row>
     <row r="116">
@@ -4122,20 +4122,20 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>0.9532</v>
+        <v>0.8584000000000001</v>
       </c>
       <c r="F116" t="n">
-        <v>2.0058</v>
+        <v>-0.0043</v>
       </c>
       <c r="G116" t="n">
-        <v>157.8821</v>
+        <v>228.0345</v>
       </c>
       <c r="H116" t="n">
-        <v>353.3325</v>
+        <v>352.9825</v>
       </c>
     </row>
     <row r="117">
@@ -4154,20 +4154,20 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>0.854</v>
+        <v>0.8389</v>
       </c>
       <c r="F117" t="n">
-        <v>2.0085</v>
+        <v>-0.0255</v>
       </c>
       <c r="G117" t="n">
-        <v>228.8811</v>
+        <v>244.8751</v>
       </c>
       <c r="H117" t="n">
-        <v>353.8</v>
+        <v>356.6909</v>
       </c>
     </row>
     <row r="118">
@@ -4186,20 +4186,20 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>0.9826</v>
+        <v>0.9688</v>
       </c>
       <c r="F118" t="n">
-        <v>1.4345</v>
+        <v>0.5334</v>
       </c>
       <c r="G118" t="n">
-        <v>79.16240000000001</v>
+        <v>99.3232</v>
       </c>
       <c r="H118" t="n">
-        <v>232.2231</v>
+        <v>240.5919</v>
       </c>
     </row>
     <row r="119">
@@ -4218,20 +4218,20 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>0.9814000000000001</v>
+        <v>0.9705</v>
       </c>
       <c r="F119" t="n">
-        <v>1.4475</v>
+        <v>0.5078</v>
       </c>
       <c r="G119" t="n">
-        <v>81.52970000000001</v>
+        <v>102.3611</v>
       </c>
       <c r="H119" t="n">
-        <v>235.6789</v>
+        <v>247.1155</v>
       </c>
     </row>
     <row r="120">
@@ -4250,20 +4250,20 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>0.9629</v>
+        <v>0.9579</v>
       </c>
       <c r="F120" t="n">
-        <v>1.5254</v>
+        <v>0.4564</v>
       </c>
       <c r="G120" t="n">
-        <v>108.3928</v>
+        <v>115.8485</v>
       </c>
       <c r="H120" t="n">
-        <v>255.3669</v>
+        <v>259.6991</v>
       </c>
     </row>
     <row r="121">
@@ -4282,20 +4282,20 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>0.9629</v>
+        <v>0.9579</v>
       </c>
       <c r="F121" t="n">
-        <v>1.5254</v>
+        <v>0.4564</v>
       </c>
       <c r="G121" t="n">
-        <v>108.3928</v>
+        <v>115.8485</v>
       </c>
       <c r="H121" t="n">
-        <v>255.3669</v>
+        <v>259.6991</v>
       </c>
     </row>
     <row r="122">
@@ -4314,20 +4314,20 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>0.976</v>
+        <v>0.9762</v>
       </c>
       <c r="F122" t="n">
-        <v>1.3874</v>
+        <v>0.5657</v>
       </c>
       <c r="G122" t="n">
-        <v>89.3669</v>
+        <v>89.0694</v>
       </c>
       <c r="H122" t="n">
-        <v>219.2825</v>
+        <v>232.1256</v>
       </c>
     </row>
     <row r="123">
@@ -4346,20 +4346,20 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>0.9817</v>
+        <v>0.9701</v>
       </c>
       <c r="F123" t="n">
-        <v>1.4477</v>
+        <v>0.5081</v>
       </c>
       <c r="G123" t="n">
-        <v>81.0861</v>
+        <v>102.7257</v>
       </c>
       <c r="H123" t="n">
-        <v>235.7436</v>
+        <v>247.0503</v>
       </c>
     </row>
     <row r="124">
@@ -4378,20 +4378,20 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>0.9762</v>
+        <v>0.9701</v>
       </c>
       <c r="F124" t="n">
-        <v>1.4428</v>
+        <v>0.5099</v>
       </c>
       <c r="G124" t="n">
-        <v>91.2178</v>
+        <v>107.5606</v>
       </c>
       <c r="H124" t="n">
-        <v>234.4268</v>
+        <v>246.5813</v>
       </c>
     </row>
     <row r="125">
@@ -4414,16 +4414,16 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>0.9722</v>
+        <v>0.9688</v>
       </c>
       <c r="F125" t="n">
-        <v>1.4296</v>
+        <v>0.5043</v>
       </c>
       <c r="G125" t="n">
-        <v>95.24509999999999</v>
+        <v>100.0381</v>
       </c>
       <c r="H125" t="n">
-        <v>230.9199</v>
+        <v>247.9989</v>
       </c>
     </row>
     <row r="126">
@@ -4442,20 +4442,20 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>0.9808</v>
+        <v>0.9624</v>
       </c>
       <c r="F126" t="n">
-        <v>1.5136</v>
+        <v>0.4259</v>
       </c>
       <c r="G126" t="n">
-        <v>87.9058</v>
+        <v>116.5863</v>
       </c>
       <c r="H126" t="n">
-        <v>252.4807</v>
+        <v>266.8751</v>
       </c>
     </row>
     <row r="127">
@@ -4474,20 +4474,20 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>0.9826</v>
+        <v>0.9349</v>
       </c>
       <c r="F127" t="n">
-        <v>1.4435</v>
+        <v>0.5031</v>
       </c>
       <c r="G127" t="n">
-        <v>80.3111</v>
+        <v>142.6494</v>
       </c>
       <c r="H127" t="n">
-        <v>234.6159</v>
+        <v>248.2861</v>
       </c>
     </row>
   </sheetData>

--- a/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_frais/trans.alpha.carotene/RANDOMSEARCH_DETAILS_trans.alpha.carotene.xlsx
+++ b/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_frais/trans.alpha.carotene/RANDOMSEARCH_DETAILS_trans.alpha.carotene.xlsx
@@ -1306,7 +1306,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -3354,7 +3354,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E92" t="n">
